--- a/backend/API_Weather/excel_scratch.xlsx
+++ b/backend/API_Weather/excel_scratch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\willh\water_dashboard\backend\API_Weather\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D7B357-54B0-4C51-B040-10448975F2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0CDA07-961C-4AB5-8CE5-6BFD81CC6B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{193F39F3-368C-4205-BED1-02E7BDD01C5F}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="142">
   <si>
     <t>wkt_geom</t>
   </si>
@@ -1612,6 +1612,14 @@
         <v>17</v>
       </c>
     </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+    </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
@@ -1619,14 +1627,6 @@
       <c r="C8" t="s">
         <v>3</v>
       </c>
-      <c r="E8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1643,27 +1643,11 @@
       <c r="A12" t="s">
         <v>84</v>
       </c>
-      <c r="E12" t="s">
-        <v>48</v>
-      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>83</v>
       </c>
-      <c r="E13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E15" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -1688,5 +1672,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>